--- a/assets/xls/Indices and Trend.xlsx
+++ b/assets/xls/Indices and Trend.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29816"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ueanorwich.sharepoint.com/sites/LET-MathsandStats/Shared Documents/Maths and Stats/Workshops/NBS JW/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F2486AF2-2628-4D40-8FF2-D356780093C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="73" documentId="8_{8FB6C184-18D3-4049-8E04-66DA3BE58D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7B12D43-0C53-4863-860E-96B37B09B902}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{2FE2A4D7-BBDF-4365-BA0A-E633F70D63E5}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2FE2A4D7-BBDF-4365-BA0A-E633F70D63E5}"/>
   </bookViews>
   <sheets>
     <sheet name="Index Numbers" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="37">
   <si>
     <t>Year</t>
   </si>
@@ -108,6 +108,12 @@
     <t>Sales</t>
   </si>
   <si>
+    <t>12-point MA</t>
+  </si>
+  <si>
+    <t>CMA</t>
+  </si>
+  <si>
     <t>Class A</t>
   </si>
   <si>
@@ -144,12 +150,6 @@
     <t>Divide the 1973 salary by the index number for 1973 (to get the value for an index of 1) and then multiply by the index for 2019.</t>
   </si>
   <si>
-    <t>12-point MA</t>
-  </si>
-  <si>
-    <t>CMA</t>
-  </si>
-  <si>
     <t>There is a seasonal trend, with sales higher in the Northern hemisphere winter months.</t>
   </si>
   <si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="&quot;£&quot;#,##0;[Red]\-&quot;£&quot;#,##0"/>
-    <numFmt numFmtId="165" formatCode="&quot;£&quot;#,##0.00;[Red]\-&quot;£&quot;#,##0.00"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="6" formatCode="&quot;£&quot;#,##0;[Red]\-&quot;£&quot;#,##0"/>
+    <numFmt numFmtId="8" formatCode="&quot;£&quot;#,##0.00;[Red]\-&quot;£&quot;#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -243,21 +243,21 @@
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="6" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -284,7 +284,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -383,9 +383,10 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>'[1]Index Numbers'!$B$43:$B$47</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>2018</c:v>
@@ -402,8 +403,8 @@
                 <c:pt idx="4">
                   <c:v>2022</c:v>
                 </c:pt>
-              </c:strCache>
-            </c:strRef>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -713,7 +714,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -812,9 +813,10 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>'[1]Moving Averages'!$B$11:$B$70</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>43101</c:v>
@@ -996,8 +998,8 @@
                 <c:pt idx="59">
                   <c:v>44896</c:v>
                 </c:pt>
-              </c:strCache>
-            </c:strRef>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -1222,9 +1224,10 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>'[1]Moving Averages'!$B$11:$B$70</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>43101</c:v>
@@ -1406,8 +1409,8 @@
                 <c:pt idx="59">
                   <c:v>44896</c:v>
                 </c:pt>
-              </c:strCache>
-            </c:strRef>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -1767,7 +1770,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -9172,14 +9175,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E65B62D-88D2-412E-86B7-A2C434D83C65}">
   <dimension ref="B20:S47"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.81640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="20" spans="17:19" ht="18.75">
+    <row r="20" spans="17:19" ht="18.5" x14ac:dyDescent="0.45">
       <c r="Q20" s="1" t="s">
         <v>0</v>
       </c>
@@ -9190,7 +9193,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="17:19" ht="18.75">
+    <row r="21" spans="17:19" ht="18.5" x14ac:dyDescent="0.45">
       <c r="Q21" s="1">
         <v>2020</v>
       </c>
@@ -9201,39 +9204,39 @@
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="17:19" ht="18.75">
+    <row r="22" spans="17:19" ht="18.5" x14ac:dyDescent="0.45">
       <c r="Q22" s="1">
         <v>2021</v>
       </c>
       <c r="R22" s="1"/>
       <c r="S22" s="1"/>
     </row>
-    <row r="23" spans="17:19" ht="18.75">
+    <row r="23" spans="17:19" ht="18.5" x14ac:dyDescent="0.45">
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
       <c r="S23" s="1"/>
     </row>
-    <row r="24" spans="17:19" ht="18.75">
+    <row r="24" spans="17:19" ht="18.5" x14ac:dyDescent="0.45">
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
     </row>
-    <row r="25" spans="17:19" ht="18.75">
+    <row r="25" spans="17:19" ht="18.5" x14ac:dyDescent="0.45">
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
     </row>
-    <row r="26" spans="17:19" ht="18.75">
+    <row r="26" spans="17:19" ht="18.5" x14ac:dyDescent="0.45">
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
     </row>
-    <row r="27" spans="17:19" ht="18.75">
+    <row r="27" spans="17:19" ht="18.5" x14ac:dyDescent="0.45">
       <c r="Q27" s="1"/>
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
     </row>
-    <row r="28" spans="17:19" ht="18.75">
+    <row r="28" spans="17:19" ht="18.5" x14ac:dyDescent="0.45">
       <c r="Q28" s="1" t="s">
         <v>0</v>
       </c>
@@ -9244,21 +9247,21 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="17:19" ht="18.75">
+    <row r="29" spans="17:19" ht="18.5" x14ac:dyDescent="0.45">
       <c r="Q29" s="1">
         <v>1990</v>
       </c>
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
     </row>
-    <row r="30" spans="17:19" ht="18.75">
+    <row r="30" spans="17:19" ht="18.5" x14ac:dyDescent="0.45">
       <c r="Q30" s="1">
         <v>2000</v>
       </c>
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
     </row>
-    <row r="42" spans="2:4" ht="18.75">
+    <row r="42" spans="2:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B42" s="1" t="s">
         <v>0</v>
       </c>
@@ -9269,7 +9272,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="2:4" ht="18.75">
+    <row r="43" spans="2:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B43" s="1">
         <v>2018</v>
       </c>
@@ -9278,7 +9281,7 @@
       </c>
       <c r="D43" s="1"/>
     </row>
-    <row r="44" spans="2:4" ht="18.75">
+    <row r="44" spans="2:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B44" s="1">
         <v>2019</v>
       </c>
@@ -9287,7 +9290,7 @@
       </c>
       <c r="D44" s="1"/>
     </row>
-    <row r="45" spans="2:4" ht="18.75">
+    <row r="45" spans="2:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B45" s="1">
         <v>2020</v>
       </c>
@@ -9296,7 +9299,7 @@
       </c>
       <c r="D45" s="1"/>
     </row>
-    <row r="46" spans="2:4" ht="18.75">
+    <row r="46" spans="2:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B46" s="1">
         <v>2021</v>
       </c>
@@ -9305,7 +9308,7 @@
       </c>
       <c r="D46" s="1"/>
     </row>
-    <row r="47" spans="2:4" ht="18.75">
+    <row r="47" spans="2:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B47" s="1">
         <v>2022</v>
       </c>
@@ -9323,13 +9326,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2139F652-1F17-4909-894B-75A37B3F496A}">
   <dimension ref="B10:F55"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="19.7109375" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.7265625" customWidth="1"/>
+    <col min="6" max="6" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="10" spans="2:6" ht="18.75">
+    <row r="10" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
@@ -9338,7 +9342,7 @@
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
     </row>
-    <row r="11" spans="2:6" ht="18.75">
+    <row r="11" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B11" s="3" t="s">
         <v>0</v>
       </c>
@@ -9355,7 +9359,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="18.75">
+    <row r="12" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B12" s="3">
         <v>2015</v>
       </c>
@@ -9370,7 +9374,7 @@
       </c>
       <c r="F12" s="3"/>
     </row>
-    <row r="13" spans="2:6" ht="18.75">
+    <row r="13" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B13" s="3">
         <v>2016</v>
       </c>
@@ -9385,7 +9389,7 @@
       </c>
       <c r="F13" s="3"/>
     </row>
-    <row r="14" spans="2:6" ht="18.75">
+    <row r="14" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B14" s="3">
         <v>2017</v>
       </c>
@@ -9400,7 +9404,7 @@
       </c>
       <c r="F14" s="3"/>
     </row>
-    <row r="15" spans="2:6" ht="18.75">
+    <row r="15" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B15" s="3">
         <v>2018</v>
       </c>
@@ -9415,14 +9419,14 @@
       </c>
       <c r="F15" s="3"/>
     </row>
-    <row r="18" spans="2:4" ht="18.75">
+    <row r="18" spans="2:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B18" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
     </row>
-    <row r="19" spans="2:4" ht="18.75">
+    <row r="19" spans="2:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B19" s="3" t="s">
         <v>0</v>
       </c>
@@ -9433,35 +9437,35 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="2:4" ht="18.75">
+    <row r="20" spans="2:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B20" s="3">
         <v>2015</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
     </row>
-    <row r="21" spans="2:4" ht="18.75">
+    <row r="21" spans="2:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B21" s="3">
         <v>2016</v>
       </c>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="2:4" ht="18.75">
+    <row r="22" spans="2:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B22" s="3">
         <v>2017</v>
       </c>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
     </row>
-    <row r="23" spans="2:4" ht="18.75">
+    <row r="23" spans="2:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B23" s="3">
         <v>2018</v>
       </c>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="33" spans="3:4" ht="18.75">
+    <row r="33" spans="3:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C33" s="1" t="s">
         <v>13</v>
       </c>
@@ -9469,19 +9473,19 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="3:4" ht="18.75">
+    <row r="34" spans="3:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C34" s="1">
         <v>2017</v>
       </c>
       <c r="D34" s="1"/>
     </row>
-    <row r="35" spans="3:4" ht="18.75">
+    <row r="35" spans="3:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C35" s="1">
         <v>2018</v>
       </c>
       <c r="D35" s="1"/>
     </row>
-    <row r="43" spans="3:4" ht="18.75">
+    <row r="43" spans="3:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C43" s="1" t="s">
         <v>15</v>
       </c>
@@ -9489,19 +9493,19 @@
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="3:4" ht="18.75">
+    <row r="44" spans="3:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C44" s="1">
         <v>2017</v>
       </c>
       <c r="D44" s="7"/>
     </row>
-    <row r="45" spans="3:4" ht="18.75">
+    <row r="45" spans="3:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C45" s="1">
         <v>2018</v>
       </c>
       <c r="D45" s="7"/>
     </row>
-    <row r="53" spans="3:5" ht="18.75">
+    <row r="53" spans="3:5" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C53" s="1" t="s">
         <v>0</v>
       </c>
@@ -9512,7 +9516,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="54" spans="3:5" ht="18.75">
+    <row r="54" spans="3:5" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C54" s="1">
         <v>1973</v>
       </c>
@@ -9523,7 +9527,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="55" spans="3:5" ht="18.75">
+    <row r="55" spans="3:5" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C55" s="1">
         <v>2019</v>
       </c>
@@ -9540,10 +9544,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0E887D1-139A-4C91-9789-2CEB6BC3567C}">
-  <dimension ref="A10:C70"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A10:E70"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="4" max="4" width="12.1796875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
         <v>17</v>
       </c>
@@ -9553,8 +9560,14 @@
       <c r="C10" s="6" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
+      <c r="D10" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1</v>
       </c>
@@ -9565,7 +9578,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>2</v>
       </c>
@@ -9576,7 +9589,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>3</v>
       </c>
@@ -9587,7 +9600,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>4</v>
       </c>
@@ -9598,7 +9611,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>5</v>
       </c>
@@ -9609,7 +9622,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>6</v>
       </c>
@@ -9620,7 +9633,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>7</v>
       </c>
@@ -9631,7 +9644,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>8</v>
       </c>
@@ -9642,7 +9655,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>9</v>
       </c>
@@ -9653,7 +9666,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>10</v>
       </c>
@@ -9664,7 +9677,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>11</v>
       </c>
@@ -9675,7 +9688,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>12</v>
       </c>
@@ -9686,7 +9699,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>13</v>
       </c>
@@ -9697,7 +9710,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>14</v>
       </c>
@@ -9708,7 +9721,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>15</v>
       </c>
@@ -9719,7 +9732,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>16</v>
       </c>
@@ -9730,7 +9743,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>17</v>
       </c>
@@ -9741,7 +9754,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>18</v>
       </c>
@@ -9752,7 +9765,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>19</v>
       </c>
@@ -9763,7 +9776,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>20</v>
       </c>
@@ -9774,7 +9787,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>21</v>
       </c>
@@ -9785,7 +9798,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>22</v>
       </c>
@@ -9796,7 +9809,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>23</v>
       </c>
@@ -9807,7 +9820,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>24</v>
       </c>
@@ -9818,7 +9831,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>25</v>
       </c>
@@ -9829,7 +9842,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>26</v>
       </c>
@@ -9840,7 +9853,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>27</v>
       </c>
@@ -9851,7 +9864,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>28</v>
       </c>
@@ -9862,7 +9875,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>29</v>
       </c>
@@ -9873,7 +9886,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>30</v>
       </c>
@@ -9884,7 +9897,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>31</v>
       </c>
@@ -9895,7 +9908,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>32</v>
       </c>
@@ -9906,7 +9919,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>33</v>
       </c>
@@ -9917,7 +9930,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>34</v>
       </c>
@@ -9928,7 +9941,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>35</v>
       </c>
@@ -9939,7 +9952,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>36</v>
       </c>
@@ -9950,7 +9963,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>37</v>
       </c>
@@ -9961,7 +9974,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>38</v>
       </c>
@@ -9972,7 +9985,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>39</v>
       </c>
@@ -9983,7 +9996,7 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>40</v>
       </c>
@@ -9994,7 +10007,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>41</v>
       </c>
@@ -10005,7 +10018,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>42</v>
       </c>
@@ -10016,7 +10029,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>43</v>
       </c>
@@ -10027,7 +10040,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>44</v>
       </c>
@@ -10038,7 +10051,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>45</v>
       </c>
@@ -10049,7 +10062,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>46</v>
       </c>
@@ -10060,7 +10073,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>47</v>
       </c>
@@ -10071,7 +10084,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>48</v>
       </c>
@@ -10082,7 +10095,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>49</v>
       </c>
@@ -10093,7 +10106,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>50</v>
       </c>
@@ -10104,7 +10117,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>51</v>
       </c>
@@ -10115,7 +10128,7 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>52</v>
       </c>
@@ -10126,7 +10139,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>53</v>
       </c>
@@ -10137,7 +10150,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>54</v>
       </c>
@@ -10148,7 +10161,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>55</v>
       </c>
@@ -10159,7 +10172,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>56</v>
       </c>
@@ -10170,7 +10183,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>57</v>
       </c>
@@ -10181,7 +10194,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>58</v>
       </c>
@@ -10192,7 +10205,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>59</v>
       </c>
@@ -10203,7 +10216,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>60</v>
       </c>
@@ -10223,20 +10236,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EF55C57-769F-40D8-9CF2-51E7E4880E9F}">
   <dimension ref="A1:H35"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="5" max="5" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>69</v>
       </c>
@@ -10244,7 +10257,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>65</v>
       </c>
@@ -10252,7 +10265,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>54</v>
       </c>
@@ -10260,7 +10273,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>66</v>
       </c>
@@ -10268,7 +10281,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>68</v>
       </c>
@@ -10276,7 +10289,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>74</v>
       </c>
@@ -10284,7 +10297,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>66</v>
       </c>
@@ -10292,7 +10305,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>68</v>
       </c>
@@ -10300,16 +10313,16 @@
         <v>26</v>
       </c>
       <c r="F9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>81</v>
       </c>
@@ -10317,10 +10330,10 @@
         <v>19</v>
       </c>
       <c r="E10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>74</v>
       </c>
@@ -10328,10 +10341,10 @@
         <v>11</v>
       </c>
       <c r="E11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>53</v>
       </c>
@@ -10339,10 +10352,10 @@
         <v>43</v>
       </c>
       <c r="E12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>60</v>
       </c>
@@ -10350,10 +10363,10 @@
         <v>32</v>
       </c>
       <c r="E13" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>67</v>
       </c>
@@ -10361,10 +10374,10 @@
         <v>53</v>
       </c>
       <c r="E14" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>68</v>
       </c>
@@ -10372,10 +10385,10 @@
         <v>62</v>
       </c>
       <c r="E15" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>63</v>
       </c>
@@ -10383,10 +10396,10 @@
         <v>54</v>
       </c>
       <c r="E16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>44</v>
       </c>
@@ -10394,10 +10407,10 @@
         <v>63</v>
       </c>
       <c r="E17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>75</v>
       </c>
@@ -10405,7 +10418,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>84</v>
       </c>
@@ -10413,7 +10426,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>52</v>
       </c>
@@ -10421,7 +10434,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>71</v>
       </c>
@@ -10429,7 +10442,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>53</v>
       </c>
@@ -10437,7 +10450,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>77</v>
       </c>
@@ -10445,7 +10458,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>70</v>
       </c>
@@ -10453,7 +10466,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>58</v>
       </c>
@@ -10461,7 +10474,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>58</v>
       </c>
@@ -10469,7 +10482,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>80</v>
       </c>
@@ -10477,7 +10490,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>64</v>
       </c>
@@ -10485,7 +10498,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>72</v>
       </c>
@@ -10493,7 +10506,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>53</v>
       </c>
@@ -10501,7 +10514,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>49</v>
       </c>
@@ -10509,22 +10522,22 @@
         <v>71</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B32">
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="2:2">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B33">
         <v>37</v>
       </c>
     </row>
-    <row r="34" spans="2:2">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B34">
         <v>71</v>
       </c>
     </row>
-    <row r="35" spans="2:2">
+    <row r="35" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B35">
         <v>61</v>
       </c>
@@ -10538,14 +10551,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90462546-8C68-4A4E-97DA-B783539853B2}">
   <dimension ref="B20:S47"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.81640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="20" spans="16:19" ht="18.75">
+    <row r="20" spans="16:19" ht="18.5" x14ac:dyDescent="0.45">
       <c r="Q20" s="1" t="s">
         <v>0</v>
       </c>
@@ -10556,7 +10569,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="16:19" ht="18.75">
+    <row r="21" spans="16:19" ht="18.5" x14ac:dyDescent="0.45">
       <c r="Q21" s="1">
         <v>2020</v>
       </c>
@@ -10567,7 +10580,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="16:19" ht="18.75">
+    <row r="22" spans="16:19" ht="18.5" x14ac:dyDescent="0.45">
       <c r="Q22" s="1">
         <v>2021</v>
       </c>
@@ -10579,33 +10592,33 @@
         <v>112.00000000000001</v>
       </c>
     </row>
-    <row r="23" spans="16:19" ht="18.75">
+    <row r="23" spans="16:19" ht="18.5" x14ac:dyDescent="0.45">
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
       <c r="S23" s="1"/>
     </row>
-    <row r="24" spans="16:19" ht="18.75">
+    <row r="24" spans="16:19" ht="18.5" x14ac:dyDescent="0.45">
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
     </row>
-    <row r="25" spans="16:19" ht="18.75">
+    <row r="25" spans="16:19" ht="18.5" x14ac:dyDescent="0.45">
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
     </row>
-    <row r="26" spans="16:19" ht="18.75">
+    <row r="26" spans="16:19" ht="18.5" x14ac:dyDescent="0.45">
       <c r="P26" s="10"/>
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
     </row>
-    <row r="27" spans="16:19" ht="18.75">
+    <row r="27" spans="16:19" ht="18.5" x14ac:dyDescent="0.45">
       <c r="Q27" s="1"/>
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
     </row>
-    <row r="28" spans="16:19" ht="18.75">
+    <row r="28" spans="16:19" ht="18.5" x14ac:dyDescent="0.45">
       <c r="Q28" s="1" t="s">
         <v>0</v>
       </c>
@@ -10616,7 +10629,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="16:19" ht="18.75">
+    <row r="29" spans="16:19" ht="18.5" x14ac:dyDescent="0.45">
       <c r="Q29" s="1">
         <v>1990</v>
       </c>
@@ -10627,7 +10640,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="16:19" ht="18.75">
+    <row r="30" spans="16:19" ht="18.5" x14ac:dyDescent="0.45">
       <c r="Q30" s="1">
         <v>2000</v>
       </c>
@@ -10639,7 +10652,7 @@
         <v>83.333333333333343</v>
       </c>
     </row>
-    <row r="42" spans="2:4" ht="18.75">
+    <row r="42" spans="2:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B42" s="1" t="s">
         <v>0</v>
       </c>
@@ -10650,7 +10663,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="2:4" ht="18.75">
+    <row r="43" spans="2:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B43" s="1">
         <v>2018</v>
       </c>
@@ -10662,7 +10675,7 @@
         <v>98.505823457294653</v>
       </c>
     </row>
-    <row r="44" spans="2:4" ht="18.75">
+    <row r="44" spans="2:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B44" s="1">
         <v>2019</v>
       </c>
@@ -10674,7 +10687,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="45" spans="2:4" ht="18.75">
+    <row r="45" spans="2:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B45" s="1">
         <v>2020</v>
       </c>
@@ -10686,7 +10699,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="2:4" ht="18.75">
+    <row r="46" spans="2:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B46" s="1">
         <v>2021</v>
       </c>
@@ -10698,7 +10711,7 @@
         <v>101.49928483857784</v>
       </c>
     </row>
-    <row r="47" spans="2:4" ht="18.75">
+    <row r="47" spans="2:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B47" s="1">
         <v>2022</v>
       </c>
@@ -10719,13 +10732,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41C1A6E8-C6F6-442A-92B5-56D539FF895E}">
   <dimension ref="B10:F56"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="19.7109375" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.7265625" customWidth="1"/>
+    <col min="6" max="6" width="14.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="10" spans="2:6" ht="18.75">
+    <row r="10" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
@@ -10734,7 +10747,7 @@
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
     </row>
-    <row r="11" spans="2:6" ht="18.75">
+    <row r="11" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B11" s="3" t="s">
         <v>0</v>
       </c>
@@ -10751,7 +10764,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="18.75">
+    <row r="12" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B12" s="3">
         <v>2015</v>
       </c>
@@ -10769,7 +10782,7 @@
         <v>3.17</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="18.75">
+    <row r="13" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B13" s="3">
         <v>2016</v>
       </c>
@@ -10787,7 +10800,7 @@
         <v>3.42</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="18.75">
+    <row r="14" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B14" s="3">
         <v>2017</v>
       </c>
@@ -10805,7 +10818,7 @@
         <v>3.7800000000000002</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="18.75">
+    <row r="15" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B15" s="3">
         <v>2018</v>
       </c>
@@ -10823,14 +10836,14 @@
         <v>4.1399999999999997</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="18.75">
+    <row r="18" spans="2:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B18" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
     </row>
-    <row r="19" spans="2:4" ht="18.75">
+    <row r="19" spans="2:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B19" s="3" t="s">
         <v>0</v>
       </c>
@@ -10841,7 +10854,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="2:4" ht="18.75">
+    <row r="20" spans="2:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B20" s="3">
         <v>2015</v>
       </c>
@@ -10854,7 +10867,7 @@
         <v>92.690058479532169</v>
       </c>
     </row>
-    <row r="21" spans="2:4" ht="18.75">
+    <row r="21" spans="2:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B21" s="3">
         <v>2016</v>
       </c>
@@ -10867,7 +10880,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="2:4" ht="18.75">
+    <row r="22" spans="2:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B22" s="3">
         <v>2017</v>
       </c>
@@ -10880,7 +10893,7 @@
         <v>110.5263157894737</v>
       </c>
     </row>
-    <row r="23" spans="2:4" ht="18.75">
+    <row r="23" spans="2:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B23" s="3">
         <v>2018</v>
       </c>
@@ -10893,7 +10906,7 @@
         <v>121.05263157894737</v>
       </c>
     </row>
-    <row r="33" spans="3:4" ht="18.75">
+    <row r="33" spans="3:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C33" s="1" t="s">
         <v>13</v>
       </c>
@@ -10901,7 +10914,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="3:4" ht="18.75">
+    <row r="34" spans="3:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C34" s="1">
         <v>2017</v>
       </c>
@@ -10910,7 +10923,7 @@
         <v>10.526315789473699</v>
       </c>
     </row>
-    <row r="35" spans="3:4" ht="18.75">
+    <row r="35" spans="3:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C35" s="1">
         <v>2018</v>
       </c>
@@ -10919,7 +10932,7 @@
         <v>21.05263157894737</v>
       </c>
     </row>
-    <row r="43" spans="3:4" ht="18.75">
+    <row r="43" spans="3:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C43" s="1" t="s">
         <v>15</v>
       </c>
@@ -10927,7 +10940,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="3:4" ht="18.75">
+    <row r="44" spans="3:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C44" s="1">
         <v>2017</v>
       </c>
@@ -10936,7 +10949,7 @@
         <v>19.242902208201905</v>
       </c>
     </row>
-    <row r="45" spans="3:4" ht="18.75">
+    <row r="45" spans="3:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C45" s="1">
         <v>2018</v>
       </c>
@@ -10945,12 +10958,12 @@
         <v>30.599369085173496</v>
       </c>
     </row>
-    <row r="53" spans="3:5" ht="18.75">
+    <row r="53" spans="3:5" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C53" s="9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="54" spans="3:5" ht="18.75">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="54" spans="3:5" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C54" s="1" t="s">
         <v>0</v>
       </c>
@@ -10961,7 +10974,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="55" spans="3:5" ht="18.75">
+    <row r="55" spans="3:5" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C55" s="1">
         <v>1973</v>
       </c>
@@ -10972,7 +10985,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="56" spans="3:5" ht="18.75">
+    <row r="56" spans="3:5" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C56" s="1">
         <v>2019</v>
       </c>
@@ -10993,12 +11006,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82BC6D57-A354-498D-A88D-C131530F02F6}">
   <dimension ref="A10:K70"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
         <v>17</v>
       </c>
@@ -11009,13 +11022,13 @@
         <v>19</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1</v>
       </c>
@@ -11028,7 +11041,7 @@
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>2</v>
       </c>
@@ -11041,7 +11054,7 @@
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>3</v>
       </c>
@@ -11054,7 +11067,7 @@
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>4</v>
       </c>
@@ -11067,7 +11080,7 @@
       <c r="D14" s="10"/>
       <c r="E14" s="10"/>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>5</v>
       </c>
@@ -11080,7 +11093,7 @@
       <c r="D15" s="10"/>
       <c r="E15" s="10"/>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>6</v>
       </c>
@@ -11096,7 +11109,7 @@
       </c>
       <c r="E16" s="10"/>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>7</v>
       </c>
@@ -11115,7 +11128,7 @@
         <v>1007.4583333333333</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>8</v>
       </c>
@@ -11134,7 +11147,7 @@
         <v>1009.25</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>9</v>
       </c>
@@ -11153,7 +11166,7 @@
         <v>1010.7916666666667</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>10</v>
       </c>
@@ -11172,7 +11185,7 @@
         <v>1012.2916666666667</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>11</v>
       </c>
@@ -11191,7 +11204,7 @@
         <v>1013.3333333333333</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>12</v>
       </c>
@@ -11210,7 +11223,7 @@
         <v>1015.375</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>13</v>
       </c>
@@ -11229,7 +11242,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>14</v>
       </c>
@@ -11248,7 +11261,7 @@
         <v>1017.375</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>15</v>
       </c>
@@ -11267,7 +11280,7 @@
         <v>1018.0416666666667</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>16</v>
       </c>
@@ -11286,7 +11299,7 @@
         <v>1018.5416666666667</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>17</v>
       </c>
@@ -11305,7 +11318,7 @@
         <v>1019.875</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>18</v>
       </c>
@@ -11324,7 +11337,7 @@
         <v>1022.375</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>19</v>
       </c>
@@ -11343,7 +11356,7 @@
         <v>1024.0833333333333</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>20</v>
       </c>
@@ -11362,7 +11375,7 @@
         <v>1025.5833333333333</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>21</v>
       </c>
@@ -11381,7 +11394,7 @@
         <v>1027.9166666666665</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>22</v>
       </c>
@@ -11400,7 +11413,7 @@
         <v>1029.4583333333335</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>23</v>
       </c>
@@ -11419,7 +11432,7 @@
         <v>1030.7916666666667</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>24</v>
       </c>
@@ -11438,7 +11451,7 @@
         <v>1032.2083333333335</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>25</v>
       </c>
@@ -11457,7 +11470,7 @@
         <v>1034.25</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>26</v>
       </c>
@@ -11476,7 +11489,7 @@
         <v>1037.4583333333335</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>27</v>
       </c>
@@ -11495,7 +11508,7 @@
         <v>1040.5416666666667</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>28</v>
       </c>
@@ -11514,7 +11527,7 @@
         <v>1042.8333333333335</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>29</v>
       </c>
@@ -11533,7 +11546,7 @@
         <v>1043.9166666666665</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>30</v>
       </c>
@@ -11552,7 +11565,7 @@
         <v>1044.4583333333333</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>31</v>
       </c>
@@ -11571,7 +11584,7 @@
         <v>1045.5</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>32</v>
       </c>
@@ -11590,7 +11603,7 @@
         <v>1047.4166666666667</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>33</v>
       </c>
@@ -11609,7 +11622,7 @@
         <v>1049.2916666666667</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>34</v>
       </c>
@@ -11628,7 +11641,7 @@
         <v>1051.5</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>35</v>
       </c>
@@ -11647,7 +11660,7 @@
         <v>1053.5416666666665</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>36</v>
       </c>
@@ -11666,7 +11679,7 @@
         <v>1055.375</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>37</v>
       </c>
@@ -11685,7 +11698,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>38</v>
       </c>
@@ -11704,7 +11717,7 @@
         <v>1058.4583333333335</v>
       </c>
     </row>
-    <row r="49" spans="1:11">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>39</v>
       </c>
@@ -11723,7 +11736,7 @@
         <v>1060.375</v>
       </c>
     </row>
-    <row r="50" spans="1:11">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>40</v>
       </c>
@@ -11742,7 +11755,7 @@
         <v>1062.2083333333333</v>
       </c>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>41</v>
       </c>
@@ -11761,7 +11774,7 @@
         <v>1064.2916666666665</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="18.75">
+    <row r="52" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A52">
         <v>42</v>
       </c>
@@ -11783,7 +11796,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="18.75">
+    <row r="53" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A53">
         <v>43</v>
       </c>
@@ -11805,7 +11818,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="54" spans="1:11">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>44</v>
       </c>
@@ -11824,7 +11837,7 @@
         <v>1067.25</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="18.75">
+    <row r="55" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A55">
         <v>45</v>
       </c>
@@ -11846,7 +11859,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="56" spans="1:11">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>46</v>
       </c>
@@ -11865,7 +11878,7 @@
         <v>1068.6666666666667</v>
       </c>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>47</v>
       </c>
@@ -11884,7 +11897,7 @@
         <v>1069.0833333333335</v>
       </c>
     </row>
-    <row r="58" spans="1:11">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>48</v>
       </c>
@@ -11903,7 +11916,7 @@
         <v>1069.2083333333335</v>
       </c>
     </row>
-    <row r="59" spans="1:11">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>49</v>
       </c>
@@ -11922,7 +11935,7 @@
         <v>1069.1666666666667</v>
       </c>
     </row>
-    <row r="60" spans="1:11">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>50</v>
       </c>
@@ -11941,7 +11954,7 @@
         <v>1069.4166666666667</v>
       </c>
     </row>
-    <row r="61" spans="1:11">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>51</v>
       </c>
@@ -11960,7 +11973,7 @@
         <v>1070.375</v>
       </c>
     </row>
-    <row r="62" spans="1:11">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>52</v>
       </c>
@@ -11979,7 +11992,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="63" spans="1:11">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>53</v>
       </c>
@@ -11998,7 +12011,7 @@
         <v>1073.25</v>
       </c>
     </row>
-    <row r="64" spans="1:11">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>54</v>
       </c>
@@ -12017,7 +12030,7 @@
         <v>1074.5416666666665</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>55</v>
       </c>
@@ -12030,7 +12043,7 @@
       <c r="D65" s="10"/>
       <c r="E65" s="10"/>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>56</v>
       </c>
@@ -12043,7 +12056,7 @@
       <c r="D66" s="10"/>
       <c r="E66" s="10"/>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>57</v>
       </c>
@@ -12056,7 +12069,7 @@
       <c r="D67" s="10"/>
       <c r="E67" s="10"/>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>58</v>
       </c>
@@ -12069,7 +12082,7 @@
       <c r="D68" s="10"/>
       <c r="E68" s="10"/>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>59</v>
       </c>
@@ -12082,7 +12095,7 @@
       <c r="D69" s="10"/>
       <c r="E69" s="10"/>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>60</v>
       </c>
@@ -12104,20 +12117,20 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EAA3655-9C72-498C-92EC-1F14FD4E40C5}">
   <dimension ref="A1:H35"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="5" max="5" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>69</v>
       </c>
@@ -12125,7 +12138,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>65</v>
       </c>
@@ -12133,7 +12146,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>54</v>
       </c>
@@ -12141,7 +12154,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>66</v>
       </c>
@@ -12149,7 +12162,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>68</v>
       </c>
@@ -12157,7 +12170,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>74</v>
       </c>
@@ -12165,7 +12178,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>66</v>
       </c>
@@ -12173,7 +12186,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>68</v>
       </c>
@@ -12181,16 +12194,16 @@
         <v>26</v>
       </c>
       <c r="F9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>81</v>
       </c>
@@ -12198,7 +12211,7 @@
         <v>19</v>
       </c>
       <c r="E10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F10">
         <f>COUNT(A2:A35)</f>
@@ -12213,7 +12226,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>74</v>
       </c>
@@ -12221,7 +12234,7 @@
         <v>11</v>
       </c>
       <c r="E11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F11">
         <f>AVERAGE(A2:A35)</f>
@@ -12236,7 +12249,7 @@
         <v>54.75</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>53</v>
       </c>
@@ -12244,7 +12257,7 @@
         <v>43</v>
       </c>
       <c r="E12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F12">
         <f>_xlfn.STDEV.S(A2:A35)</f>
@@ -12259,7 +12272,7 @@
         <v>18.850287354131588</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>60</v>
       </c>
@@ -12267,7 +12280,7 @@
         <v>32</v>
       </c>
       <c r="E13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F13">
         <f>MEDIAN(A2:A35)</f>
@@ -12282,7 +12295,7 @@
         <v>59.5</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>67</v>
       </c>
@@ -12290,7 +12303,7 @@
         <v>53</v>
       </c>
       <c r="E14" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F14">
         <f>MIN(A2:A35)</f>
@@ -12305,7 +12318,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>68</v>
       </c>
@@ -12313,7 +12326,7 @@
         <v>62</v>
       </c>
       <c r="E15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F15">
         <f>MAX(A2:A35)</f>
@@ -12328,7 +12341,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>63</v>
       </c>
@@ -12336,7 +12349,7 @@
         <v>54</v>
       </c>
       <c r="E16" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F16">
         <f>F15-F14</f>
@@ -12351,7 +12364,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>44</v>
       </c>
@@ -12359,7 +12372,7 @@
         <v>63</v>
       </c>
       <c r="E17" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F17">
         <f>_xlfn.QUARTILE.EXC(A2:A35,3)-_xlfn.QUARTILE.EXC(A2:A35,1)</f>
@@ -12374,7 +12387,7 @@
         <v>24.75</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>75</v>
       </c>
@@ -12382,7 +12395,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>84</v>
       </c>
@@ -12390,7 +12403,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>52</v>
       </c>
@@ -12398,7 +12411,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>71</v>
       </c>
@@ -12406,7 +12419,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>53</v>
       </c>
@@ -12414,7 +12427,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>77</v>
       </c>
@@ -12422,7 +12435,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>70</v>
       </c>
@@ -12430,7 +12443,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>58</v>
       </c>
@@ -12438,7 +12451,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>58</v>
       </c>
@@ -12446,7 +12459,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>80</v>
       </c>
@@ -12454,7 +12467,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>64</v>
       </c>
@@ -12462,7 +12475,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>72</v>
       </c>
@@ -12470,7 +12483,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>53</v>
       </c>
@@ -12478,7 +12491,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>49</v>
       </c>
@@ -12486,22 +12499,22 @@
         <v>71</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B32">
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="2:2">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B33">
         <v>37</v>
       </c>
     </row>
-    <row r="34" spans="2:2">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B34">
         <v>71</v>
       </c>
     </row>
-    <row r="35" spans="2:2">
+    <row r="35" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B35">
         <v>61</v>
       </c>
@@ -12513,8 +12526,19 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010069F3779B66BC3F4DAB5120B5380EDEF8" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b8cbbc459aadea2f4567da3449623fb4">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="34cc328e-f486-4d73-9163-9d26e8cf8d6e" xmlns:ns3="686c71fa-6862-4526-b774-d8add1c96eee" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="acfa781aaebca2a615833601c5c2a0c3" ns2:_="" ns3:_="">
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="34cc328e-f486-4d73-9163-9d26e8cf8d6e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="686c71fa-6862-4526-b774-d8add1c96eee" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010069F3779B66BC3F4DAB5120B5380EDEF8" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8ae092d07ffbfac35db9a706e6a16320">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="34cc328e-f486-4d73-9163-9d26e8cf8d6e" xmlns:ns3="686c71fa-6862-4526-b774-d8add1c96eee" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="def645eeacd6dc86ff9e2f96a401f5c2" ns2:_="" ns3:_="">
     <xsd:import namespace="34cc328e-f486-4d73-9163-9d26e8cf8d6e"/>
     <xsd:import namespace="686c71fa-6862-4526-b774-d8add1c96eee"/>
     <xsd:element name="properties">
@@ -12761,7 +12785,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -12770,25 +12794,40 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="34cc328e-f486-4d73-9163-9d26e8cf8d6e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="686c71fa-6862-4526-b774-d8add1c96eee" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31F2239C-2C59-405A-86BC-5E4D80892A10}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFFCA92F-9FA2-448E-ADFA-F4937D02565D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="34cc328e-f486-4d73-9163-9d26e8cf8d6e"/>
+    <ds:schemaRef ds:uri="686c71fa-6862-4526-b774-d8add1c96eee"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1F378D9-0FBC-4EE8-970E-4E249D36EFFC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59F26C0B-4427-4152-9ABA-736B4A81E4F1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="34cc328e-f486-4d73-9163-9d26e8cf8d6e"/>
+    <ds:schemaRef ds:uri="686c71fa-6862-4526-b774-d8add1c96eee"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFFCA92F-9FA2-448E-ADFA-F4937D02565D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1F378D9-0FBC-4EE8-970E-4E249D36EFFC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/assets/xls/Indices and Trend.xlsx
+++ b/assets/xls/Indices and Trend.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ueanorwich.sharepoint.com/sites/LET-MathsandStats/Shared Documents/Maths and Stats/Workshops/NBS JW/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="73" documentId="8_{8FB6C184-18D3-4049-8E04-66DA3BE58D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7B12D43-0C53-4863-860E-96B37B09B902}"/>
+  <xr:revisionPtr revIDLastSave="100" documentId="8_{8FB6C184-18D3-4049-8E04-66DA3BE58D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC99FF52-87D3-4A4A-AD87-96BE52F4734C}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2FE2A4D7-BBDF-4365-BA0A-E633F70D63E5}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{2FE2A4D7-BBDF-4365-BA0A-E633F70D63E5}"/>
   </bookViews>
   <sheets>
     <sheet name="Index Numbers" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="38">
   <si>
     <t>Year</t>
   </si>
@@ -158,6 +158,9 @@
   <si>
     <t>The trend of the sales is a gradual rise</t>
   </si>
+  <si>
+    <t>NBS-4107B</t>
+  </si>
 </sst>
 </file>
 
@@ -240,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="6" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -264,6 +267,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="8" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -296,31 +300,6 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-GB"/>
-              <a:t>Salaries</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -361,7 +340,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'[1]Index Numbers'!$D$42</c:f>
+              <c:f>'Solutions Index Numbers'!$D$42</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -384,10 +363,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'[1]Index Numbers'!$B$43:$B$47</c:f>
+              <c:f>'Solutions Index Numbers'!$B$43:$B$50</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>2018</c:v>
                 </c:pt>
@@ -402,16 +381,25 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2025</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'[1]Index Numbers'!$D$43:$D$47</c:f>
+              <c:f>'Solutions Index Numbers'!$D$43:$D$50</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>98.505823457294653</c:v>
                 </c:pt>
@@ -422,10 +410,19 @@
                   <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>101.49928483857779</c:v>
+                  <c:v>101.49928483857784</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>104.54382917858599</c:v>
+                  <c:v>104.54382917858602</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="General">
+                  <c:v>108</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="General">
+                  <c:v>110.09</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="General">
+                  <c:v>115.1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -433,7 +430,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-B879-45B1-A5A3-FE034202C7DF}"/>
+              <c16:uniqueId val="{00000000-C615-4913-8906-ED61F4FB5A6D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -446,71 +443,16 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="861478912"/>
-        <c:axId val="861479992"/>
+        <c:axId val="553368488"/>
+        <c:axId val="553364168"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="861478912"/>
+        <c:axId val="553368488"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-GB"/>
-                  <a:t>Year</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -548,7 +490,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="861479992"/>
+        <c:crossAx val="553364168"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -556,7 +498,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="861479992"/>
+        <c:axId val="553364168"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -576,62 +518,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-GB"/>
-                  <a:t>Index (2020 = 100)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -662,7 +549,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="861478912"/>
+        <c:crossAx val="553368488"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4295,7 +4182,31 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>The following shows the salary for a particular job over some years.  Using 2020 as the base year, calculate the index numbers for the salaries</a:t>
+            <a:t>The following shows the salary for a particular job over some years.  Using 2020 as the base year, calculate the missing index numbers and</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1800" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1800">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>salaries</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
@@ -6136,23 +6047,7 @@
           </a:lvl9pPr>
         </a:lstStyle>
         <a:p>
-          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClrTx/>
-            <a:buSzTx/>
-            <a:buFontTx/>
-            <a:buNone/>
-            <a:tabLst/>
-            <a:defRPr/>
-          </a:pPr>
+          <a:pPr eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1"/>
           <a:r>
             <a:rPr lang="en-GB" sz="1800">
               <a:solidFill>
@@ -6163,8 +6058,35 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>The following shows the salary for a particular job over some years.  Using 2020 as the base year, calculate the index numbers for the salaries.  Draw a line chart of the index number against the year.</a:t>
+            <a:t>The following shows the salary for a particular job over some years.  Using 2020 as the base year, calculate the missing index numbers and</a:t>
           </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1800" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1800">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>salaries.  Draw a line chart of the index number against the year.</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="1800">
+            <a:effectLst/>
+          </a:endParaRPr>
         </a:p>
         <a:p>
           <a:endParaRPr lang="en-GB" sz="1100"/>
@@ -6175,32 +6097,27 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>447674</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>4762</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>6356</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>323849</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>33337</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>447675</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>82556</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="6" name="Chart 5">
+        <xdr:cNvPr id="7" name="Chart 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1E72DA6-4A18-472F-A2E8-E60378941017}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{C89A6932-CD19-4735-8EEE-DE20237AB03C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{763AF39E-4AA7-AB57-426C-99F260C2B5AD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
+        <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -9174,7 +9091,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E65B62D-88D2-412E-86B7-A2C434D83C65}">
-  <dimension ref="B20:S47"/>
+  <dimension ref="A1:S50"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="10.54296875" bestFit="1" customWidth="1"/>
@@ -9182,6 +9099,11 @@
     <col min="18" max="18" width="13.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>37</v>
+      </c>
+    </row>
     <row r="20" spans="17:19" ht="18.5" x14ac:dyDescent="0.45">
       <c r="Q20" s="1" t="s">
         <v>0</v>
@@ -9316,6 +9238,30 @@
         <v>40931</v>
       </c>
       <c r="D47" s="1"/>
+    </row>
+    <row r="48" spans="2:4" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B48" s="1">
+        <v>2023</v>
+      </c>
+      <c r="D48" s="1">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B49" s="1">
+        <v>2024</v>
+      </c>
+      <c r="D49" s="1">
+        <v>110.09</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B50" s="1">
+        <v>2025</v>
+      </c>
+      <c r="D50" s="1">
+        <v>115.1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10550,10 +10496,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90462546-8C68-4A4E-97DA-B783539853B2}">
-  <dimension ref="B20:S47"/>
+  <dimension ref="B20:S50"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.453125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.81640625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13.453125" bestFit="1" customWidth="1"/>
   </cols>
@@ -10723,9 +10669,46 @@
         <v>104.54382917858602</v>
       </c>
     </row>
+    <row r="48" spans="2:4" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B48" s="1">
+        <v>2023</v>
+      </c>
+      <c r="C48" s="15">
+        <f>D48*$C$45/100</f>
+        <v>42284.160000000003</v>
+      </c>
+      <c r="D48" s="1">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B49" s="1">
+        <v>2024</v>
+      </c>
+      <c r="C49" s="15">
+        <f t="shared" ref="C49:C50" si="1">D49*$C$45/100</f>
+        <v>43102.436799999996</v>
+      </c>
+      <c r="D49" s="1">
+        <v>110.09</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B50" s="1">
+        <v>2025</v>
+      </c>
+      <c r="C50" s="15">
+        <f t="shared" si="1"/>
+        <v>45063.952000000005</v>
+      </c>
+      <c r="D50" s="1">
+        <v>115.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -12526,14 +12509,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="34cc328e-f486-4d73-9163-9d26e8cf8d6e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="686c71fa-6862-4526-b774-d8add1c96eee" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12786,21 +12767,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="34cc328e-f486-4d73-9163-9d26e8cf8d6e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="686c71fa-6862-4526-b774-d8add1c96eee" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFFCA92F-9FA2-448E-ADFA-F4937D02565D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1F378D9-0FBC-4EE8-970E-4E249D36EFFC}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="34cc328e-f486-4d73-9163-9d26e8cf8d6e"/>
-    <ds:schemaRef ds:uri="686c71fa-6862-4526-b774-d8add1c96eee"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -12825,9 +12805,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1F378D9-0FBC-4EE8-970E-4E249D36EFFC}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFFCA92F-9FA2-448E-ADFA-F4937D02565D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="34cc328e-f486-4d73-9163-9d26e8cf8d6e"/>
+    <ds:schemaRef ds:uri="686c71fa-6862-4526-b774-d8add1c96eee"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>